--- a/research/traditional_assets/database/data/netherlands/netherlands_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0363</v>
+        <v>0.0351</v>
       </c>
       <c r="E2">
-        <v>0.161</v>
+        <v>-0.0275</v>
       </c>
       <c r="F2">
-        <v>-0.02545</v>
+        <v>0.079335</v>
       </c>
       <c r="G2">
-        <v>0.05087374648030575</v>
+        <v>0.3321917619050249</v>
       </c>
       <c r="H2">
-        <v>0.05087374648030575</v>
+        <v>0.3321917619050249</v>
       </c>
       <c r="I2">
-        <v>0.06933774671210721</v>
+        <v>0.1121296812185075</v>
       </c>
       <c r="J2">
-        <v>0.05888702415844524</v>
+        <v>0.1025717853904322</v>
       </c>
       <c r="K2">
-        <v>4649.8</v>
+        <v>4362.3</v>
       </c>
       <c r="L2">
-        <v>0.05140439532011945</v>
+        <v>0.2409617923407922</v>
       </c>
       <c r="M2">
-        <v>2192.4</v>
+        <v>2524.6</v>
       </c>
       <c r="N2">
-        <v>0.08191172184985093</v>
+        <v>0.1158068082256504</v>
       </c>
       <c r="O2">
-        <v>0.4715041507161598</v>
+        <v>0.5787314031588842</v>
       </c>
       <c r="P2">
-        <v>1101.7</v>
+        <v>720.1</v>
       </c>
       <c r="Q2">
-        <v>0.04116135010125012</v>
+        <v>0.03303195856899739</v>
       </c>
       <c r="R2">
-        <v>0.2369349219321261</v>
+        <v>0.1650734704169819</v>
       </c>
       <c r="S2">
-        <v>1090.7</v>
+        <v>1804.5</v>
       </c>
       <c r="T2">
-        <v>0.4974913336982302</v>
+        <v>0.7147666957141724</v>
       </c>
       <c r="U2">
-        <v>15811.1</v>
+        <v>14412.5</v>
       </c>
       <c r="V2">
-        <v>0.5907290755975998</v>
+        <v>0.6611208205466947</v>
       </c>
       <c r="W2">
-        <v>0.06346572391680846</v>
+        <v>0.05453270343013961</v>
       </c>
       <c r="X2">
-        <v>0.08725123245527061</v>
+        <v>0.1287536443262863</v>
       </c>
       <c r="Y2">
-        <v>-0.02378550853846215</v>
+        <v>-0.07422094089614673</v>
       </c>
       <c r="Z2">
-        <v>1.312930679366802</v>
+        <v>0.221696899924495</v>
       </c>
       <c r="AA2">
-        <v>0.07406670802058979</v>
+        <v>0.01727992815870438</v>
       </c>
       <c r="AB2">
-        <v>0.05308603740624469</v>
+        <v>0.08144138463731053</v>
       </c>
       <c r="AC2">
-        <v>0.0209806706143451</v>
+        <v>-0.06416145647860616</v>
       </c>
       <c r="AD2">
-        <v>26914.5</v>
+        <v>26199.3</v>
       </c>
       <c r="AE2">
-        <v>52.61659916164985</v>
+        <v>47.18945062253059</v>
       </c>
       <c r="AF2">
-        <v>26967.11659916165</v>
+        <v>26246.48945062253</v>
       </c>
       <c r="AG2">
-        <v>11156.01659916165</v>
+        <v>11833.98945062253</v>
       </c>
       <c r="AH2">
-        <v>0.5018770440315167</v>
+        <v>0.546271644891591</v>
       </c>
       <c r="AI2">
-        <v>0.2733615008777487</v>
+        <v>0.4089066908304417</v>
       </c>
       <c r="AJ2">
-        <v>0.2941877598372283</v>
+        <v>0.351845096564774</v>
       </c>
       <c r="AK2">
-        <v>0.1346712035496919</v>
+        <v>0.2377521011513765</v>
       </c>
       <c r="AL2">
-        <v>1029.7</v>
+        <v>964.5</v>
       </c>
       <c r="AM2">
-        <v>1029.7</v>
+        <v>964.5</v>
       </c>
       <c r="AN2">
-        <v>3.714450536787062</v>
+        <v>13.7572463768116</v>
       </c>
       <c r="AO2">
-        <v>6.091774303195106</v>
+        <v>2.105028512182478</v>
       </c>
       <c r="AP2">
-        <v>1.539633723277838</v>
+        <v>6.214025126350836</v>
       </c>
       <c r="AQ2">
-        <v>6.091774303195106</v>
+        <v>2.105028512182478</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0581</v>
+        <v>0.0351</v>
       </c>
       <c r="E3">
-        <v>0.161</v>
+        <v>0.252</v>
       </c>
       <c r="F3">
-        <v>-0.08210000000000001</v>
+        <v>0.006670000000000001</v>
       </c>
       <c r="G3">
-        <v>0.1764736326819317</v>
+        <v>0.2187398156178019</v>
       </c>
       <c r="H3">
-        <v>0.1764736326819317</v>
+        <v>0.2187398156178019</v>
       </c>
       <c r="I3">
-        <v>0.1892098214863344</v>
+        <v>0.1280180294635903</v>
       </c>
       <c r="J3">
-        <v>0.1587231544678303</v>
+        <v>0.1061936030239206</v>
       </c>
       <c r="K3">
-        <v>3238.1</v>
+        <v>4045.6</v>
       </c>
       <c r="L3">
-        <v>0.1396581543093</v>
+        <v>0.2234681308240857</v>
       </c>
       <c r="M3">
-        <v>1524.8</v>
+        <v>1447.9</v>
       </c>
       <c r="N3">
-        <v>0.09115255858440938</v>
+        <v>0.1203494364464541</v>
       </c>
       <c r="O3">
-        <v>0.4708934251567277</v>
+        <v>0.3578949970338146</v>
       </c>
       <c r="P3">
-        <v>902.3</v>
+        <v>511.2</v>
       </c>
       <c r="Q3">
-        <v>0.05393950263032042</v>
+        <v>0.04249093992086977</v>
       </c>
       <c r="R3">
-        <v>0.2786510608072635</v>
+        <v>0.1263595016808385</v>
       </c>
       <c r="S3">
-        <v>622.5</v>
+        <v>936.7</v>
       </c>
       <c r="T3">
-        <v>0.4082502623294859</v>
+        <v>0.6469369431590579</v>
       </c>
       <c r="U3">
-        <v>8444.4</v>
+        <v>6516.8</v>
       </c>
       <c r="V3">
-        <v>0.50480631276901</v>
+        <v>0.5416763639990692</v>
       </c>
       <c r="W3">
-        <v>0.07801785826149391</v>
+        <v>0.09853762141834159</v>
       </c>
       <c r="X3">
-        <v>0.07875400123412241</v>
+        <v>0.1279582015073051</v>
       </c>
       <c r="Y3">
-        <v>-0.0007361429726285007</v>
+        <v>-0.02942058008896346</v>
       </c>
       <c r="Z3">
-        <v>0.5815783400890959</v>
+        <v>0.399881164587047</v>
       </c>
       <c r="AA3">
-        <v>0.09230994870910592</v>
+        <v>0.04246482164889992</v>
       </c>
       <c r="AB3">
-        <v>0.05354925928997976</v>
+        <v>0.08148234137896709</v>
       </c>
       <c r="AC3">
-        <v>0.03876068941912615</v>
+        <v>-0.03901751973006717</v>
       </c>
       <c r="AD3">
-        <v>13290.3</v>
+        <v>14241.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>13290.3</v>
+        <v>14241.1</v>
       </c>
       <c r="AG3">
-        <v>4845.9</v>
+        <v>7724.3</v>
       </c>
       <c r="AH3">
-        <v>0.4427399286435275</v>
+        <v>0.5420658574370335</v>
       </c>
       <c r="AI3">
-        <v>0.2430301833382706</v>
+        <v>0.3835098132149859</v>
       </c>
       <c r="AJ3">
-        <v>0.2246186364078817</v>
+        <v>0.3910028296490527</v>
       </c>
       <c r="AK3">
-        <v>0.1047957025522584</v>
+        <v>0.2522895926419482</v>
       </c>
       <c r="AL3">
-        <v>589.3</v>
+        <v>593.8</v>
       </c>
       <c r="AM3">
-        <v>589.3</v>
+        <v>593.8</v>
       </c>
       <c r="AN3">
-        <v>2.987457009913008</v>
+        <v>5.967108019777089</v>
       </c>
       <c r="AO3">
-        <v>7.444425589682675</v>
+        <v>3.902997642303806</v>
       </c>
       <c r="AP3">
-        <v>1.089284510081597</v>
+        <v>3.236528953322719</v>
       </c>
       <c r="AQ3">
-        <v>7.444425589682675</v>
+        <v>3.902997642303806</v>
       </c>
     </row>
     <row r="4">
@@ -861,122 +861,107 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.0145</v>
+      <c r="E4">
+        <v>-0.307</v>
       </c>
       <c r="F4">
-        <v>0.0312</v>
-      </c>
-      <c r="G4">
-        <v>0.007582942615810459</v>
-      </c>
-      <c r="H4">
-        <v>0.007582942615810459</v>
-      </c>
-      <c r="I4">
-        <v>0.02802116088693626</v>
-      </c>
-      <c r="J4">
-        <v>0.02408929540135423</v>
+        <v>0.152</v>
       </c>
       <c r="K4">
-        <v>1411.7</v>
-      </c>
-      <c r="L4">
-        <v>0.02098576767445525</v>
+        <v>316.7</v>
       </c>
       <c r="M4">
-        <v>667.6</v>
+        <v>1076.7</v>
       </c>
       <c r="N4">
-        <v>0.06651124793273158</v>
+        <v>0.1102126047925645</v>
       </c>
       <c r="O4">
-        <v>0.4729050081462067</v>
+        <v>3.399747395011052</v>
       </c>
       <c r="P4">
-        <v>199.4</v>
+        <v>208.9</v>
       </c>
       <c r="Q4">
-        <v>0.01986570227349712</v>
+        <v>0.02138331303163993</v>
       </c>
       <c r="R4">
-        <v>0.1412481405397747</v>
+        <v>0.6596147773918535</v>
       </c>
       <c r="S4">
-        <v>468.2</v>
+        <v>867.8000000000001</v>
       </c>
       <c r="T4">
-        <v>0.701318154583583</v>
+        <v>0.8059812389709298</v>
       </c>
       <c r="U4">
-        <v>7366.7</v>
+        <v>7895.7</v>
       </c>
       <c r="V4">
-        <v>0.7339251200510092</v>
+        <v>0.8082155323308733</v>
       </c>
       <c r="W4">
-        <v>0.04891358957212304</v>
+        <v>0.01052778544193762</v>
       </c>
       <c r="X4">
-        <v>0.09574846367641882</v>
+        <v>0.1295490871452676</v>
       </c>
       <c r="Y4">
-        <v>-0.04683487410429578</v>
+        <v>-0.11902130170333</v>
       </c>
       <c r="Z4">
-        <v>2.317355754993789</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>0.05582346733207366</v>
+        <v>-0.007904965331491171</v>
       </c>
       <c r="AB4">
-        <v>0.05262281552250961</v>
+        <v>0.08140042789565397</v>
       </c>
       <c r="AC4">
-        <v>0.003200651809564053</v>
+        <v>-0.08930539322714513</v>
       </c>
       <c r="AD4">
-        <v>13624.2</v>
+        <v>11958.2</v>
       </c>
       <c r="AE4">
-        <v>52.61659916164985</v>
+        <v>47.18945062253059</v>
       </c>
       <c r="AF4">
-        <v>13676.81659916165</v>
+        <v>12005.38945062253</v>
       </c>
       <c r="AG4">
-        <v>6310.11659916165</v>
+        <v>4109.689450622532</v>
       </c>
       <c r="AH4">
-        <v>0.5767349109750965</v>
+        <v>0.5513460698416207</v>
       </c>
       <c r="AI4">
-        <v>0.311089737453037</v>
+        <v>0.4437665554822474</v>
       </c>
       <c r="AJ4">
-        <v>0.3859984824536133</v>
+        <v>0.296108694746374</v>
       </c>
       <c r="AK4">
-        <v>0.1724192564286233</v>
+        <v>0.2145190557146748</v>
       </c>
       <c r="AL4">
-        <v>440.4</v>
+        <v>370.7</v>
       </c>
       <c r="AM4">
-        <v>440.4</v>
+        <v>370.7</v>
       </c>
       <c r="AN4">
-        <v>4.870673783332559</v>
+        <v>-24.79925342181668</v>
       </c>
       <c r="AO4">
-        <v>4.281789282470482</v>
+        <v>-0.7750202319935258</v>
       </c>
       <c r="AP4">
-        <v>2.255877004837587</v>
+        <v>-8.522790233559792</v>
       </c>
       <c r="AQ4">
-        <v>4.281789282470482</v>
+        <v>-0.7750202319935258</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0351</v>
+        <v>0.0286</v>
       </c>
       <c r="E2">
-        <v>-0.0275</v>
+        <v>-0.293</v>
       </c>
       <c r="F2">
-        <v>0.079335</v>
+        <v>0.04635</v>
       </c>
       <c r="G2">
-        <v>0.3321917619050249</v>
+        <v>-0.04551828106890152</v>
       </c>
       <c r="H2">
-        <v>0.3321917619050249</v>
+        <v>-0.04551828106890152</v>
       </c>
       <c r="I2">
-        <v>0.1121296812185075</v>
+        <v>0.2707528826895481</v>
       </c>
       <c r="J2">
-        <v>0.1025717853904322</v>
+        <v>0.240500415024781</v>
       </c>
       <c r="K2">
-        <v>4362.3</v>
+        <v>-2540.4</v>
       </c>
       <c r="L2">
-        <v>0.2409617923407922</v>
+        <v>-0.1029510694688723</v>
       </c>
       <c r="M2">
-        <v>2524.6</v>
+        <v>2996.8</v>
       </c>
       <c r="N2">
-        <v>0.1158068082256504</v>
+        <v>0.1388242923982026</v>
       </c>
       <c r="O2">
-        <v>0.5787314031588842</v>
+        <v>-1.179656746968982</v>
       </c>
       <c r="P2">
-        <v>720.1</v>
+        <v>1044.8</v>
       </c>
       <c r="Q2">
-        <v>0.03303195856899739</v>
+        <v>0.04839949969889286</v>
       </c>
       <c r="R2">
-        <v>0.1650734704169819</v>
+        <v>-0.4112738151472211</v>
       </c>
       <c r="S2">
-        <v>1804.5</v>
+        <v>1952</v>
       </c>
       <c r="T2">
-        <v>0.7147666957141724</v>
+        <v>0.6513614522156967</v>
       </c>
       <c r="U2">
-        <v>14412.5</v>
+        <v>11957.4</v>
       </c>
       <c r="V2">
-        <v>0.6611208205466947</v>
+        <v>0.5539167091304953</v>
       </c>
       <c r="W2">
-        <v>0.05453270343013961</v>
+        <v>-0.0638204307644791</v>
       </c>
       <c r="X2">
-        <v>0.1287536443262863</v>
+        <v>0.1006332726218668</v>
       </c>
       <c r="Y2">
-        <v>-0.07422094089614673</v>
+        <v>-0.1644537033863459</v>
       </c>
       <c r="Z2">
-        <v>0.221696899924495</v>
+        <v>0.4571854806746337</v>
       </c>
       <c r="AA2">
-        <v>0.01727992815870438</v>
+        <v>0.07163749828522292</v>
       </c>
       <c r="AB2">
-        <v>0.08144138463731053</v>
+        <v>0.06993566838227294</v>
       </c>
       <c r="AC2">
-        <v>-0.06416145647860616</v>
+        <v>0.001701829902949981</v>
       </c>
       <c r="AD2">
-        <v>26199.3</v>
+        <v>21196.5</v>
       </c>
       <c r="AE2">
-        <v>47.18945062253059</v>
+        <v>48.78008664624094</v>
       </c>
       <c r="AF2">
-        <v>26246.48945062253</v>
+        <v>21245.28008664624</v>
       </c>
       <c r="AG2">
-        <v>11833.98945062253</v>
+        <v>9287.880086646241</v>
       </c>
       <c r="AH2">
-        <v>0.546271644891591</v>
+        <v>0.4960109535067654</v>
       </c>
       <c r="AI2">
-        <v>0.4089066908304417</v>
+        <v>0.3847905686223246</v>
       </c>
       <c r="AJ2">
-        <v>0.351845096564774</v>
+        <v>0.3008231954450039</v>
       </c>
       <c r="AK2">
-        <v>0.2377521011513765</v>
+        <v>0.2147229549857683</v>
       </c>
       <c r="AL2">
-        <v>964.5</v>
+        <v>4507.7</v>
       </c>
       <c r="AM2">
-        <v>964.5</v>
+        <v>4507.7</v>
       </c>
       <c r="AN2">
-        <v>13.7572463768116</v>
+        <v>3.077353039387912</v>
       </c>
       <c r="AO2">
-        <v>2.105028512182478</v>
+        <v>1.481930918206624</v>
       </c>
       <c r="AP2">
-        <v>6.214025126350836</v>
+        <v>1.348434223296831</v>
       </c>
       <c r="AQ2">
-        <v>2.105028512182478</v>
+        <v>1.481930918206624</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0351</v>
+        <v>0.0286</v>
       </c>
       <c r="E3">
-        <v>0.252</v>
+        <v>-0.293</v>
       </c>
       <c r="F3">
-        <v>0.006670000000000001</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="G3">
-        <v>0.2187398156178019</v>
+        <v>0.02143800808889681</v>
       </c>
       <c r="H3">
-        <v>0.2187398156178019</v>
+        <v>0.02143800808889681</v>
       </c>
       <c r="I3">
-        <v>0.1280180294635903</v>
+        <v>0.3594655492425778</v>
       </c>
       <c r="J3">
-        <v>0.1061936030239206</v>
+        <v>0.279136063572591</v>
       </c>
       <c r="K3">
-        <v>4045.6</v>
+        <v>444.3</v>
       </c>
       <c r="L3">
-        <v>0.2234681308240857</v>
+        <v>0.01800549526256494</v>
       </c>
       <c r="M3">
-        <v>1447.9</v>
+        <v>1742.4</v>
       </c>
       <c r="N3">
-        <v>0.1203494364464541</v>
+        <v>0.1596701030927835</v>
       </c>
       <c r="O3">
-        <v>0.3578949970338146</v>
+        <v>3.921674544226874</v>
       </c>
       <c r="P3">
-        <v>511.2</v>
+        <v>543.7</v>
       </c>
       <c r="Q3">
-        <v>0.04249093992086977</v>
+        <v>0.04982359679266896</v>
       </c>
       <c r="R3">
-        <v>0.1263595016808385</v>
+        <v>1.223722709880711</v>
       </c>
       <c r="S3">
-        <v>936.7</v>
+        <v>1198.7</v>
       </c>
       <c r="T3">
-        <v>0.6469369431590579</v>
+        <v>0.6879591368227732</v>
       </c>
       <c r="U3">
-        <v>6516.8</v>
+        <v>7858.1</v>
       </c>
       <c r="V3">
-        <v>0.5416763639990692</v>
+        <v>0.7201008018327606</v>
       </c>
       <c r="W3">
-        <v>0.09853762141834159</v>
+        <v>0.01960049056370711</v>
       </c>
       <c r="X3">
-        <v>0.1279582015073051</v>
+        <v>0.1118770359494755</v>
       </c>
       <c r="Y3">
-        <v>-0.02942058008896346</v>
+        <v>-0.09227654538576835</v>
       </c>
       <c r="Z3">
-        <v>0.399881164587047</v>
+        <v>0.8345920862603706</v>
       </c>
       <c r="AA3">
-        <v>0.04246482164889992</v>
+        <v>0.2329647496475561</v>
       </c>
       <c r="AB3">
-        <v>0.08148234137896709</v>
+        <v>0.06859264823189982</v>
       </c>
       <c r="AC3">
-        <v>-0.03901751973006717</v>
+        <v>0.1643721014156563</v>
       </c>
       <c r="AD3">
-        <v>14241.1</v>
+        <v>15306.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>14241.1</v>
+        <v>15306.8</v>
       </c>
       <c r="AG3">
-        <v>7724.3</v>
+        <v>7448.699999999999</v>
       </c>
       <c r="AH3">
-        <v>0.5420658574370335</v>
+        <v>0.5837989572566773</v>
       </c>
       <c r="AI3">
-        <v>0.3835098132149859</v>
+        <v>0.4018977952702152</v>
       </c>
       <c r="AJ3">
-        <v>0.3910028296490527</v>
+        <v>0.4056760996013333</v>
       </c>
       <c r="AK3">
-        <v>0.2522895926419482</v>
+        <v>0.2464155986793788</v>
       </c>
       <c r="AL3">
-        <v>593.8</v>
+        <v>4028.4</v>
       </c>
       <c r="AM3">
-        <v>593.8</v>
+        <v>4028.4</v>
       </c>
       <c r="AN3">
-        <v>5.967108019777089</v>
+        <v>1.711136450019004</v>
       </c>
       <c r="AO3">
-        <v>3.902997642303806</v>
+        <v>2.201891569854036</v>
       </c>
       <c r="AP3">
-        <v>3.236528953322719</v>
+        <v>0.8326849553960693</v>
       </c>
       <c r="AQ3">
-        <v>3.902997642303806</v>
+        <v>2.201891569854036</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aegon N.V. (ENXTAM:AGN)</t>
+          <t>Aegon Ltd. (ENXTAM:AGN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -861,107 +861,104 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="E4">
-        <v>-0.307</v>
-      </c>
       <c r="F4">
-        <v>0.152</v>
+        <v>0.0384</v>
       </c>
       <c r="K4">
-        <v>316.7</v>
+        <v>-2984.7</v>
       </c>
       <c r="M4">
-        <v>1076.7</v>
+        <v>1254.4</v>
       </c>
       <c r="N4">
-        <v>0.1102126047925645</v>
+        <v>0.1175137008759193</v>
       </c>
       <c r="O4">
-        <v>3.399747395011052</v>
+        <v>-0.4202767447314639</v>
       </c>
       <c r="P4">
-        <v>208.9</v>
+        <v>501.1</v>
       </c>
       <c r="Q4">
-        <v>0.02138331303163993</v>
+        <v>0.04694365075647571</v>
       </c>
       <c r="R4">
-        <v>0.6596147773918535</v>
+        <v>-0.1678895701410527</v>
       </c>
       <c r="S4">
-        <v>867.8000000000001</v>
+        <v>753.3000000000001</v>
       </c>
       <c r="T4">
-        <v>0.8059812389709298</v>
+        <v>0.6005261479591837</v>
       </c>
       <c r="U4">
-        <v>7895.7</v>
+        <v>4099.3</v>
       </c>
       <c r="V4">
-        <v>0.8082155323308733</v>
+        <v>0.3840273549112371</v>
       </c>
       <c r="W4">
-        <v>0.01052778544193762</v>
+        <v>-0.1472413520926653</v>
       </c>
       <c r="X4">
-        <v>0.1295490871452676</v>
+        <v>0.08938950929425821</v>
       </c>
       <c r="Y4">
-        <v>-0.11902130170333</v>
+        <v>-0.2366308613869235</v>
       </c>
       <c r="Z4">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>-0.007904965331491171</v>
+        <v>-0.08968975307711026</v>
       </c>
       <c r="AB4">
-        <v>0.08140042789565397</v>
+        <v>0.07127868853264606</v>
       </c>
       <c r="AC4">
-        <v>-0.08930539322714513</v>
+        <v>-0.1609684416097563</v>
       </c>
       <c r="AD4">
-        <v>11958.2</v>
+        <v>5889.7</v>
       </c>
       <c r="AE4">
-        <v>47.18945062253059</v>
+        <v>48.78008664624094</v>
       </c>
       <c r="AF4">
-        <v>12005.38945062253</v>
+        <v>5938.480086646241</v>
       </c>
       <c r="AG4">
-        <v>4109.689450622532</v>
+        <v>1839.180086646241</v>
       </c>
       <c r="AH4">
-        <v>0.5513460698416207</v>
+        <v>0.3574602543116078</v>
       </c>
       <c r="AI4">
-        <v>0.4437665554822474</v>
+        <v>0.3467466406366092</v>
       </c>
       <c r="AJ4">
-        <v>0.296108694746374</v>
+        <v>0.1469735580509918</v>
       </c>
       <c r="AK4">
-        <v>0.2145190557146748</v>
+        <v>0.1411823825946857</v>
       </c>
       <c r="AL4">
-        <v>370.7</v>
+        <v>479.3</v>
       </c>
       <c r="AM4">
-        <v>370.7</v>
+        <v>479.3</v>
       </c>
       <c r="AN4">
-        <v>-24.79925342181668</v>
+        <v>-2.862551640340218</v>
       </c>
       <c r="AO4">
-        <v>-0.7750202319935258</v>
+        <v>-4.569163363238055</v>
       </c>
       <c r="AP4">
-        <v>-8.522790233559792</v>
+        <v>-0.8938906860978084</v>
       </c>
       <c r="AQ4">
-        <v>-0.7750202319935258</v>
+        <v>-4.569163363238055</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0286</v>
+        <v>-0.165</v>
       </c>
       <c r="E2">
-        <v>-0.293</v>
+        <v>-0.0211</v>
       </c>
       <c r="F2">
-        <v>0.04635</v>
+        <v>0.1655</v>
       </c>
       <c r="G2">
-        <v>-0.04551828106890152</v>
+        <v>0.07134227352821941</v>
       </c>
       <c r="H2">
-        <v>-0.04551828106890152</v>
+        <v>0.07134227352821941</v>
       </c>
       <c r="I2">
-        <v>0.2707528826895481</v>
+        <v>0.05874679393265552</v>
       </c>
       <c r="J2">
-        <v>0.240500415024781</v>
+        <v>0.05234956245926245</v>
       </c>
       <c r="K2">
-        <v>-2540.4</v>
+        <v>1290.1</v>
       </c>
       <c r="L2">
-        <v>-0.1029510694688723</v>
+        <v>0.05178275406703942</v>
       </c>
       <c r="M2">
-        <v>2996.8</v>
+        <v>3233.6</v>
       </c>
       <c r="N2">
-        <v>0.1388242923982026</v>
+        <v>0.1500176294839201</v>
       </c>
       <c r="O2">
-        <v>-1.179656746968982</v>
+        <v>2.506472366483218</v>
       </c>
       <c r="P2">
-        <v>1044.8</v>
+        <v>951.4</v>
       </c>
       <c r="Q2">
-        <v>0.04839949969889286</v>
+        <v>0.0441386605303691</v>
       </c>
       <c r="R2">
-        <v>-0.4112738151472211</v>
+        <v>0.7374622122316099</v>
       </c>
       <c r="S2">
-        <v>1952</v>
+        <v>2282.2</v>
       </c>
       <c r="T2">
-        <v>0.6513614522156967</v>
+        <v>0.705776843146957</v>
       </c>
       <c r="U2">
-        <v>11957.4</v>
+        <v>11456.1</v>
       </c>
       <c r="V2">
-        <v>0.5539167091304953</v>
+        <v>0.5314871861487928</v>
       </c>
       <c r="W2">
-        <v>-0.0638204307644791</v>
+        <v>0.02767004694532058</v>
       </c>
       <c r="X2">
-        <v>0.1006332726218668</v>
+        <v>0.09969225232898003</v>
       </c>
       <c r="Y2">
-        <v>-0.1644537033863459</v>
+        <v>-0.07202220538365944</v>
       </c>
       <c r="Z2">
-        <v>0.4571854806746337</v>
+        <v>0.5932921035523179</v>
       </c>
       <c r="AA2">
-        <v>0.07163749828522292</v>
+        <v>0.01320040894001444</v>
       </c>
       <c r="AB2">
-        <v>0.06993566838227294</v>
+        <v>0.07385570938583524</v>
       </c>
       <c r="AC2">
-        <v>0.001701829902949981</v>
+        <v>-0.06065530044582081</v>
       </c>
       <c r="AD2">
-        <v>21196.5</v>
+        <v>18039.2</v>
       </c>
       <c r="AE2">
-        <v>48.78008664624094</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>21245.28008664624</v>
+        <v>18039.2</v>
       </c>
       <c r="AG2">
-        <v>9287.880086646241</v>
+        <v>6583.1</v>
       </c>
       <c r="AH2">
-        <v>0.4960109535067654</v>
+        <v>0.4556043845027025</v>
       </c>
       <c r="AI2">
-        <v>0.3847905686223246</v>
+        <v>0.3608309080180424</v>
       </c>
       <c r="AJ2">
-        <v>0.3008231954450039</v>
+        <v>0.2339584688267426</v>
       </c>
       <c r="AK2">
-        <v>0.2147229549857683</v>
+        <v>0.1708236673984234</v>
       </c>
       <c r="AL2">
-        <v>4507.7</v>
+        <v>479.99</v>
       </c>
       <c r="AM2">
-        <v>4507.7</v>
+        <v>479.99</v>
       </c>
       <c r="AN2">
-        <v>3.077353039387912</v>
+        <v>10.08170793047561</v>
       </c>
       <c r="AO2">
-        <v>1.481930918206624</v>
+        <v>3.049230192295672</v>
       </c>
       <c r="AP2">
-        <v>1.348434223296831</v>
+        <v>3.679148270273291</v>
       </c>
       <c r="AQ2">
-        <v>1.481930918206624</v>
+        <v>3.049230192295672</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0286</v>
+        <v>-0.122</v>
       </c>
       <c r="E3">
-        <v>-0.293</v>
+        <v>-0.0211</v>
       </c>
       <c r="F3">
-        <v>0.05429999999999999</v>
+        <v>0.111</v>
       </c>
       <c r="G3">
-        <v>0.02143800808889681</v>
+        <v>0.1555679711957148</v>
       </c>
       <c r="H3">
-        <v>0.02143800808889681</v>
+        <v>0.1555679711957148</v>
       </c>
       <c r="I3">
-        <v>0.3594655492425778</v>
+        <v>0.1519408306063267</v>
       </c>
       <c r="J3">
-        <v>0.279136063572591</v>
+        <v>0.1188496404806993</v>
       </c>
       <c r="K3">
-        <v>444.3</v>
+        <v>1322.2</v>
       </c>
       <c r="L3">
-        <v>0.01800549526256494</v>
+        <v>0.1172568529899522</v>
       </c>
       <c r="M3">
-        <v>1742.4</v>
+        <v>1221.4</v>
       </c>
       <c r="N3">
-        <v>0.1596701030927835</v>
+        <v>0.1023659662914757</v>
       </c>
       <c r="O3">
-        <v>3.921674544226874</v>
+        <v>0.9237634245953714</v>
       </c>
       <c r="P3">
-        <v>543.7</v>
+        <v>598.9</v>
       </c>
       <c r="Q3">
-        <v>0.04982359679266896</v>
+        <v>0.05019402096935055</v>
       </c>
       <c r="R3">
-        <v>1.223722709880711</v>
+        <v>0.4529571925578581</v>
       </c>
       <c r="S3">
-        <v>1198.7</v>
+        <v>622.5000000000001</v>
       </c>
       <c r="T3">
-        <v>0.6879591368227732</v>
+        <v>0.5096610447028002</v>
       </c>
       <c r="U3">
-        <v>7858.1</v>
+        <v>7283.8</v>
       </c>
       <c r="V3">
-        <v>0.7201008018327606</v>
+        <v>0.6104578559635258</v>
       </c>
       <c r="W3">
-        <v>0.01960049056370711</v>
+        <v>0.05825567818826691</v>
       </c>
       <c r="X3">
-        <v>0.1118770359494755</v>
+        <v>0.1069772803948513</v>
       </c>
       <c r="Y3">
-        <v>-0.09227654538576835</v>
+        <v>-0.04872160220658441</v>
       </c>
       <c r="Z3">
-        <v>0.8345920862603706</v>
+        <v>0.3862723133998581</v>
       </c>
       <c r="AA3">
-        <v>0.2329647496475561</v>
+        <v>0.04590832557522113</v>
       </c>
       <c r="AB3">
-        <v>0.06859264823189982</v>
+        <v>0.07248248700675688</v>
       </c>
       <c r="AC3">
-        <v>0.1643721014156563</v>
+        <v>-0.02657416143153575</v>
       </c>
       <c r="AD3">
-        <v>15306.8</v>
+        <v>13086.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15306.8</v>
+        <v>13086.9</v>
       </c>
       <c r="AG3">
-        <v>7448.699999999999</v>
+        <v>5803.099999999999</v>
       </c>
       <c r="AH3">
-        <v>0.5837989572566773</v>
+        <v>0.5230868234033879</v>
       </c>
       <c r="AI3">
-        <v>0.4018977952702152</v>
+        <v>0.3654262314765432</v>
       </c>
       <c r="AJ3">
-        <v>0.4056760996013333</v>
+        <v>0.3272154182736766</v>
       </c>
       <c r="AK3">
-        <v>0.2464155986793788</v>
+        <v>0.2034112776868369</v>
       </c>
       <c r="AL3">
-        <v>4028.4</v>
+        <v>4.29</v>
       </c>
       <c r="AM3">
-        <v>4028.4</v>
+        <v>4.29</v>
       </c>
       <c r="AN3">
-        <v>1.711136450019004</v>
+        <v>7.313977533113508</v>
       </c>
       <c r="AO3">
-        <v>2.201891569854036</v>
+        <v>399.3706293706293</v>
       </c>
       <c r="AP3">
-        <v>0.8326849553960693</v>
+        <v>3.243223606997149</v>
       </c>
       <c r="AQ3">
-        <v>2.201891569854036</v>
+        <v>399.3706293706293</v>
       </c>
     </row>
     <row r="4">
@@ -861,104 +861,116 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.208</v>
+      </c>
       <c r="F4">
-        <v>0.0384</v>
+        <v>0.22</v>
+      </c>
+      <c r="G4">
+        <v>0.001701179093095559</v>
+      </c>
+      <c r="H4">
+        <v>0.001701179093095559</v>
+      </c>
+      <c r="I4">
+        <v>-0.01830967325629143</v>
+      </c>
+      <c r="J4">
+        <v>-0.01830967325629143</v>
       </c>
       <c r="K4">
-        <v>-2984.7</v>
+        <v>-32.1</v>
+      </c>
+      <c r="L4">
+        <v>-0.002353786590015839</v>
       </c>
       <c r="M4">
-        <v>1254.4</v>
+        <v>2012.2</v>
       </c>
       <c r="N4">
-        <v>0.1175137008759193</v>
+        <v>0.2091010173436834</v>
       </c>
       <c r="O4">
-        <v>-0.4202767447314639</v>
+        <v>-62.68535825545171</v>
       </c>
       <c r="P4">
-        <v>501.1</v>
+        <v>352.5</v>
       </c>
       <c r="Q4">
-        <v>0.04694365075647571</v>
+        <v>0.03663060760046139</v>
       </c>
       <c r="R4">
-        <v>-0.1678895701410527</v>
+        <v>-10.98130841121495</v>
       </c>
       <c r="S4">
-        <v>753.3000000000001</v>
+        <v>1659.7</v>
       </c>
       <c r="T4">
-        <v>0.6005261479591837</v>
+        <v>0.8248186065003479</v>
       </c>
       <c r="U4">
-        <v>4099.3</v>
+        <v>4172.3</v>
       </c>
       <c r="V4">
-        <v>0.3840273549112371</v>
+        <v>0.4335713023869647</v>
       </c>
       <c r="W4">
-        <v>-0.1472413520926653</v>
+        <v>-0.002915584297625752</v>
       </c>
       <c r="X4">
-        <v>0.08938950929425821</v>
+        <v>0.09240722426310874</v>
       </c>
       <c r="Y4">
-        <v>-0.2366308613869235</v>
+        <v>-0.0953228085607345</v>
       </c>
       <c r="Z4">
+        <v>1.065420852799175</v>
+      </c>
+      <c r="AA4">
+        <v>-0.01950750769519226</v>
+      </c>
+      <c r="AB4">
+        <v>0.0752289317649136</v>
+      </c>
+      <c r="AC4">
+        <v>-0.09473643946010586</v>
+      </c>
+      <c r="AD4">
+        <v>4952.3</v>
+      </c>
+      <c r="AE4">
         <v>0</v>
       </c>
-      <c r="AA4">
-        <v>-0.08968975307711026</v>
-      </c>
-      <c r="AB4">
-        <v>0.07127868853264606</v>
-      </c>
-      <c r="AC4">
-        <v>-0.1609684416097563</v>
-      </c>
-      <c r="AD4">
-        <v>5889.7</v>
-      </c>
-      <c r="AE4">
-        <v>48.78008664624094</v>
-      </c>
       <c r="AF4">
-        <v>5938.480086646241</v>
+        <v>4952.3</v>
       </c>
       <c r="AG4">
-        <v>1839.180086646241</v>
+        <v>780</v>
       </c>
       <c r="AH4">
-        <v>0.3574602543116078</v>
+        <v>0.3397711212042208</v>
       </c>
       <c r="AI4">
-        <v>0.3467466406366092</v>
+        <v>0.3492257136409794</v>
       </c>
       <c r="AJ4">
-        <v>0.1469735580509918</v>
+        <v>0.07497765089252242</v>
       </c>
       <c r="AK4">
-        <v>0.1411823825946857</v>
+        <v>0.07793375630713893</v>
       </c>
       <c r="AL4">
-        <v>479.3</v>
+        <v>475.7</v>
       </c>
       <c r="AM4">
-        <v>479.3</v>
-      </c>
-      <c r="AN4">
-        <v>-2.862551640340218</v>
+        <v>475.7</v>
       </c>
       <c r="AO4">
-        <v>-4.569163363238055</v>
-      </c>
-      <c r="AP4">
-        <v>-0.8938906860978084</v>
+        <v>-0.5249106579777171</v>
       </c>
       <c r="AQ4">
-        <v>-4.569163363238055</v>
+        <v>-0.5249106579777171</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_insurance_life.xlsx
@@ -648,10 +648,10 @@
         <v>0.02767004694532058</v>
       </c>
       <c r="X2">
-        <v>0.09969225232898003</v>
+        <v>0.09965760440232127</v>
       </c>
       <c r="Y2">
-        <v>-0.07202220538365944</v>
+        <v>-0.07198755745700069</v>
       </c>
       <c r="Z2">
         <v>0.5932921035523179</v>
@@ -660,10 +660,10 @@
         <v>0.01320040894001444</v>
       </c>
       <c r="AB2">
-        <v>0.07385570938583524</v>
+        <v>0.07383643886960048</v>
       </c>
       <c r="AC2">
-        <v>-0.06065530044582081</v>
+        <v>-0.06063602992958605</v>
       </c>
       <c r="AD2">
         <v>18039.2</v>
@@ -785,10 +785,10 @@
         <v>0.05825567818826691</v>
       </c>
       <c r="X3">
-        <v>0.1069772803948513</v>
+        <v>0.1069379488428619</v>
       </c>
       <c r="Y3">
-        <v>-0.04872160220658441</v>
+        <v>-0.04868227065459501</v>
       </c>
       <c r="Z3">
         <v>0.3862723133998581</v>
@@ -797,10 +797,10 @@
         <v>0.04590832557522113</v>
       </c>
       <c r="AB3">
-        <v>0.07248248700675688</v>
+        <v>0.07246372927135714</v>
       </c>
       <c r="AC3">
-        <v>-0.02657416143153575</v>
+        <v>-0.026555403696136</v>
       </c>
       <c r="AD3">
         <v>13086.9</v>
@@ -919,10 +919,10 @@
         <v>-0.002915584297625752</v>
       </c>
       <c r="X4">
-        <v>0.09240722426310874</v>
+        <v>0.09237725996178062</v>
       </c>
       <c r="Y4">
-        <v>-0.0953228085607345</v>
+        <v>-0.09529284425940637</v>
       </c>
       <c r="Z4">
         <v>1.065420852799175</v>
@@ -931,10 +931,10 @@
         <v>-0.01950750769519226</v>
       </c>
       <c r="AB4">
-        <v>0.0752289317649136</v>
+        <v>0.07520914846784384</v>
       </c>
       <c r="AC4">
-        <v>-0.09473643946010586</v>
+        <v>-0.09471665616303609</v>
       </c>
       <c r="AD4">
         <v>4952.3</v>
